--- a/data/burr_ct_dataset.xlsx
+++ b/data/burr_ct_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Burr ML Project\Burr-prediction--using-ml\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E895A766-D6E6-4249-A09A-BBEE5B1E1B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9771AF-72F9-43BE-B405-35C52C74A8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9273C5A2-27BD-42A8-8063-BC93ADEE553A}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{9273C5A2-27BD-42A8-8063-BC93ADEE553A}"/>
   </bookViews>
   <sheets>
     <sheet name="burr CT" sheetId="1" r:id="rId1"/>
